--- a/administrative_forms/026_immigration_compliance_declaration_form--administrative_forms.xlsx
+++ b/administrative_forms/026_immigration_compliance_declaration_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,91 +520,103 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_header</t>
+          <t>employee_id</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Form Header</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your current employee ID?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter your employee ID as it appears on your passport or national ID</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_section_1_title</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Form Section 1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is your department?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select your department</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_section_1_employee_name</t>
+          <t>employee_status</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Employee Name</t>
+          <t>What is your employment status?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Enter your name as it appears on your passport or national ID</t>
+          <t>Select your status</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_section_1_employee_id</t>
+          <t>employment_start_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Employee ID</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is your start date of employment?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MM/DD/YYYY</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -616,18 +628,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_section_1_department</t>
+          <t>section_and_subsection</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is your section and subsection in the company's organizational structure?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter your section and subsection</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -639,18 +655,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_section_2</t>
+          <t>employee_name</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Form Section 2</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What is your name as it appears on your passport or national ID?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter your name as it appears on your passport or national ID</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -662,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_section_2_section</t>
+          <t>section_and_subsection_6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is your section and subsection for form section 6?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter your section and subsection</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -685,18 +709,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_section_2_subsection</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Subsection</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What is your role in the company?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enter your role</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -708,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_section_3</t>
+          <t>subsection_7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Form Section 3</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is your subsection for form section 7?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter your subsection</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -726,23 +758,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_section_3_employee_status</t>
+          <t>job_title</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Employee Status</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is your job title?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enter your job title</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -754,12 +790,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_section_3_employment_start_date</t>
+          <t>date_of_birth</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Employment Start Date</t>
+          <t>What is your date of birth?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -769,7 +805,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -781,18 +817,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_section_4</t>
+          <t>nationality</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Form Section 4</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What is your nationality?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Enter your nationality</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -804,18 +844,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>form_section_4_section</t>
+          <t>passport_number</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>What is your passport number?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Enter your passport number</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -827,18 +871,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>form_section_4_subsection</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Subsection</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>What is your address?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Enter your address</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -850,18 +898,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>form_section_5</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Form Section 5</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>What is your contact email?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Enter your contact email</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -873,225 +925,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>form_section_5_section</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>What is your contact phone number?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Enter your contact phone number</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>form_section_5_subsection</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Subsection</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>form_section_6</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Form Section 6</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>form_section_6_section</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>form_section_6_subsection</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Subsection</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_section_7</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Form Section 7</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_section_7_section</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>form_section_7_subsection</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Subsection</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_section_8</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Form Section 8</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_section_8_section</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1106,12 +955,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1134,49 +983,151 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_section_3_employee_status_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_section_3_employee_status_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_section_3_employee_status_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>department_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>department_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>department_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>employee_status_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>employee_status_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>employee_status_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>retired</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Retired</t>
         </is>
